--- a/results/block3_results/segment stenosis/Synthetic_2/stenosis_summary_Synthetic_2.xlsx
+++ b/results/block3_results/segment stenosis/Synthetic_2/stenosis_summary_Synthetic_2.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>74.99885670204935</v>
+        <v>73.67258943306337</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
